--- a/testcase/极致节能功能测试用例.xlsx
+++ b/testcase/极致节能功能测试用例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="覆盖说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -873,7 +873,7 @@
       </c>
       <c r="K8" s="7" t="inlineStr">
         <is>
-          <t>打开“极致节能说明”弹窗；说明平台定时反复下发指令实现刚性节能；列出生效日期/生效时间/周运行时间内执行、排除日期不执行、下发间隔1-120分钟、四个控制项均可选且至少设置一项等规则。</t>
+          <t>打开“极致节能说明”弹窗；说明平台定时反复下发指令实现刚性节能；列出生效日期/生效时间/周运行时间内执行、排除日期不执行、下发间隔5-120分钟且用于避免频繁控制、四个控制项均可选且至少设置一项等规则。</t>
         </is>
       </c>
       <c r="L8" s="5" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="K70" s="7" t="inlineStr">
         <is>
-          <t>下发间隔默认15，旁注“分钟（ 1-120 分钟）”；下方展示示例文案“设定生效时间 08:00 至 12:00、下发间隔 30 分钟，则将在 08:00、08:30、09:00 … 11:30 各下发一次控制指令”。</t>
+          <t>下发间隔默认15，旁注“分钟（ 5-120 分钟）”；下方展示示例文案“设定生效时间 08:00 至 12:00、下发间隔 30 分钟，则将在 08:00、08:30、09:00 … 11:30 各下发一次控制指令”。</t>
         </is>
       </c>
       <c r="L70" s="5" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>下发间隔=1保存成功</t>
+          <t>下发间隔=5保存成功</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
@@ -4885,18 +4885,18 @@
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
-          <t>间隔=1；名称=间隔1；温度=26</t>
+          <t>间隔=5；名称=间隔5；温度=26</t>
         </is>
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>1. 设置间隔为1
+          <t>1. 设置间隔为5
 2. 保存</t>
         </is>
       </c>
       <c r="K71" s="7" t="inlineStr">
         <is>
-          <t>保存成功；提示与控制策略列均显示“每 1 分钟”。</t>
+          <t>保存成功；提示与控制策略列均显示“每 5 分钟”。</t>
         </is>
       </c>
       <c r="L71" s="5" t="inlineStr">
@@ -4993,7 +4993,7 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>下发间隔=0</t>
+          <t>下发间隔=4</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
@@ -5013,18 +5013,18 @@
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>间隔=0；名称=间隔0；温度=26</t>
+          <t>间隔=4；名称=间隔4；温度=26</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>1. 设置间隔为0
+          <t>1. 设置间隔为4
 2. 保存</t>
         </is>
       </c>
       <c r="K73" s="7" t="inlineStr">
         <is>
-          <t>错误框显示“下发间隔请输入 1-120 分钟的整数”，任务未保存。</t>
+          <t>错误框显示“下发间隔请输入 5-120 分钟的整数”，任务未保存。</t>
         </is>
       </c>
       <c r="L73" s="5" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>错误框显示“下发间隔请输入 1-120 分钟的整数”，任务未保存。</t>
+          <t>错误框显示“下发间隔请输入 5-120 分钟的整数”，任务未保存。</t>
         </is>
       </c>
       <c r="L74" s="5" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="K75" s="7" t="inlineStr">
         <is>
-          <t>错误框显示“下发间隔请输入 1-120 分钟的整数”，任务未保存。</t>
+          <t>错误框显示“下发间隔请输入 5-120 分钟的整数”，任务未保存。</t>
         </is>
       </c>
       <c r="L75" s="5" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>错误框显示“下发间隔请输入 1-120 分钟的整数”，任务未保存。</t>
+          <t>错误框显示“下发间隔请输入 5-120 分钟的整数”，任务未保存。</t>
         </is>
       </c>
       <c r="L76" s="5" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>下发间隔1-120边界与异常、开关机/模式/风速选项、温度可选与边界、至少设置一项、指令文本拼接</t>
+          <t>下发间隔5-120边界与异常、开关机/模式/风速选项、温度可选与边界、至少设置一项、指令文本拼接</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>下发间隔 1-120 分钟整数（旧版1440已收紧）；温度 16-30℃、最多1位小数、可为空；生效时间5分钟粒度，结束可选24:00（分钟锁定00）；任务名称≤30字；任务描述≤200字；排除日期须在生效日期范围内。</t>
+          <t>下发间隔 5-120 分钟整数（旧版1440已收紧）；温度 16-30℃、最多1位小数、可为空；生效时间5分钟粒度，结束可选24:00（分钟锁定00）；任务名称≤30字；任务描述≤200字；排除日期须在生效日期范围内。</t>
         </is>
       </c>
     </row>

--- a/testcase/极致节能功能测试用例.xlsx
+++ b/testcase/极致节能功能测试用例.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="测试用例" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="覆盖说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -6579,7 +6579,7 @@
       </c>
       <c r="K97" s="7" t="inlineStr">
         <is>
-          <t>打开“空调控制指令记录”弹窗；显示3条记录，含下发时间、下发内容和“成功/部分成功”状态标签。</t>
+          <t>打开“空调控制指令记录”弹窗；显示6条记录，仅记录空调控制动作与执行结果（不体现房间信息，房间范围以任务为准）；含时间、控制指令内容和“成功/异常”状态标签，指令参数随任务配置；成功记录文本为“执行空调控制：开机 / 制冷 / 26℃ / 高风。”；异常（含下发失败/部分下发失败）记录文本为“执行空调控制：开机 / 制冷 / 26℃ / 高风，部分空调（1-2-1-2、1-2-1-3）由于【设备离线】未执行成功。”，【】内失败原因按实际情况填写（示例含设备离线、状态锁定两种），全部下发失败时文本为“…，全部空调由于【设备离线】未执行成功。”。</t>
         </is>
       </c>
       <c r="L97" s="5" t="inlineStr">
@@ -6591,7 +6591,7 @@
       <c r="N97" s="7" t="n"/>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>原型为静态演示日志</t>
+          <t>原型为演示日志，指令内容随任务配置生成</t>
         </is>
       </c>
     </row>

--- a/testcase/极致节能功能测试用例.xlsx
+++ b/testcase/极致节能功能测试用例.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
-          <t>默认2条任务</t>
+          <t>默认10条任务</t>
         </is>
       </c>
       <c r="J6" s="7" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="K6" s="7" t="inlineStr">
         <is>
-          <t>显示2条默认任务（午休时段定时节能、深夜恒温控制）；列包含复选框、任务名称、生效日期、生效时间、控制策略、最后修改时间、任务状态、操作。</t>
+          <t>显示10条默认任务（午休时段定时节能、深夜恒温控制等）；列包含复选框、任务名称、生效日期、生效时间、控制策略、最后修改时间、任务状态、操作。</t>
         </is>
       </c>
       <c r="L6" s="5" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>默认2条任务</t>
+          <t>默认10条任务</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>1. 观察两条任务的“控制策略”列</t>
+          <t>1. 观察前两条任务的“控制策略”列</t>
         </is>
       </c>
       <c r="K7" s="7" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="K12" s="7" t="inlineStr">
         <is>
-          <t>两条默认任务的房间范围均包含901会议室，列表仍显示2条任务。</t>
+          <t>午休时段定时节能、深夜恒温控制、凌晨防冻保温的房间范围均包含901会议室，列表显示该3条任务。</t>
         </is>
       </c>
       <c r="L12" s="5" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
-          <t>生效日期起=2027-01-01</t>
+          <t>生效日期起=2027-03-01</t>
         </is>
       </c>
       <c r="J16" s="7" t="inlineStr">
@@ -1382,7 +1382,7 @@
       </c>
       <c r="K16" s="7" t="inlineStr">
         <is>
-          <t>两条默认任务的结束日期均为2026-12-31，早于查询起始日期，显示“暂无数据”。</t>
+          <t>全部默认任务的结束日期均不晚于2027-02-28，早于查询起始日期，显示“暂无数据”。</t>
         </is>
       </c>
       <c r="L16" s="5" t="inlineStr">
@@ -6836,7 +6836,7 @@
       </c>
       <c r="K101" s="7" t="inlineStr">
         <is>
-          <t>任务列表恢复为2条默认任务。</t>
+          <t>任务列表恢复为10条默认任务。</t>
         </is>
       </c>
       <c r="L101" s="5" t="inlineStr">
